--- a/tables/simulation_parameters.xlsx
+++ b/tables/simulation_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\SIM\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AA777B7-71BC-41E4-BE2A-C9670BFB624E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C04D196-4F68-4922-B940-BA75F10CB585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,24 +49,12 @@
     <t>$N$</t>
   </si>
   <si>
-    <t>Total of IRS reflecting elements</t>
-  </si>
-  <si>
     <t>\acs{MCS}</t>
   </si>
   <si>
-    <t>\acl{MCS}</t>
-  </si>
-  <si>
     <t>$f_c$</t>
   </si>
   <si>
-    <t>\ac{AP}'s location</t>
-  </si>
-  <si>
-    <t>\ac{MU}'s initial location</t>
-  </si>
-  <si>
     <t>$P_\mathrm{N}$</t>
   </si>
   <si>
@@ -76,9 +64,6 @@
     <t>$v$</t>
   </si>
   <si>
-    <t>\ac{MU}'s speed</t>
-  </si>
-  <si>
     <t>$f_s$</t>
   </si>
   <si>
@@ -101,9 +86,6 @@
   </si>
   <si>
     <t>Transmitter peak power</t>
-  </si>
-  <si>
-    <t>$\mathbf{p}_\mathrm{IRS}$</t>
   </si>
   <si>
     <t>$\mathbf{p}_\mathrm{MU}$</t>
@@ -218,10 +200,28 @@
     <t>\textcolor{red}{$\approx \SI{-70}{\decibelm}$}</t>
   </si>
   <si>
-    <t>\ac{SIM}'s location</t>
-  </si>
-  <si>
     <t>\textcolor{red}{$\SI{1}{\meter\per\second}$}</t>
+  </si>
+  <si>
+    <t>\acs{AP}'s location</t>
+  </si>
+  <si>
+    <t>\acs{SIM}'s location</t>
+  </si>
+  <si>
+    <t>\acs{MU}'s initial location</t>
+  </si>
+  <si>
+    <t>\acs{MU}'s speed</t>
+  </si>
+  <si>
+    <t>Total of \acs{SIM} reflecting elements</t>
+  </si>
+  <si>
+    <t>$\mathbf{p}_\mathrm{SIM}$</t>
+  </si>
+  <si>
+    <t>Modulation and conding scheme</t>
   </si>
 </sst>
 </file>
@@ -640,7 +640,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="8.7265625" style="1"/>
-    <col min="3" max="3" width="14.26953125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.453125" style="1" customWidth="1"/>
     <col min="4" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
@@ -658,241 +658,241 @@
     </row>
     <row r="2" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="6" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="8"/>
       <c r="C3" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A4" s="8"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="8"/>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="8"/>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="9"/>
       <c r="B7" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="11"/>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="C13" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="11"/>
       <c r="C14" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="11"/>
       <c r="C15" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11"/>
       <c r="B16" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="11"/>
       <c r="B17" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" s="11"/>
       <c r="B18" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="12"/>
       <c r="B19" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B20" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B22" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="4"/>
       <c r="B23" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
